--- a/backend/backups/category6_smart_home_security_FINAL.xlsx
+++ b/backend/backups/category6_smart_home_security_FINAL.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -507,12 +507,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c979bf9e-4b28-47ad-8c79-2d91e2cce3b2</t>
+          <t>b542de45-1772-55c6-831a-1857e2534465</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CCTV Camera Installation</t>
+          <t>Alarm &amp; Sensor Systems Service Variation 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Security Systems</t>
+          <t>Alarm &amp; Sensor Systems</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1499</v>
+        <v>1200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,22 +535,1472 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Mounting of up to 4 CCTV cameras (Dome/Bullet)", "Routing and clipping of BNC/CAT6 cables up to 20 meters per camera", "Connection to DVR/NVR and power supply", "Configuration of recording settings (continuous/motion-based)", "Mobile app installation and pairing on up to 2 devices"]</t>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional installation and configuration of IP or Analog CCTV cameras, including optimal placement for blind-spot coverage, secure wiring routing, DVR/NVR setup, and mobile app pairing for remote live viewing.", "type": "description"}, {"type": "highlights", "items": ["Optimal angle positioning to eliminate security blind spots", "Concealed or neatly clipped wiring to maintain home aesthetics", "DVR/NVR storage configuration for maximum video retention", "Mobile application setup for real-time remote monitoring", "Night vision and motion detection calibration"]}, {"type": "excluded_scope", "items": ["Supply of cameras, DVR/NVR, cables, or storage hard drives (labor only)", "Concealed internal wall wiring requiring masonry/chasing", "Setting up static IP configurations with ISP for older DVR models"]}, {"type": "process_steps", "steps": [{"title": "Site Assessment &amp; Angle Planning", "description": "Technician surveys the property to identify critical entry points and determine the optimal mounting locations and angles for maximum coverage.", "is_key_step": true, "step_number": 1}, {"title": "Camera Mounting &amp; Wiring", "description": "Cameras are securely drilled and mounted. Cables are routed from the cameras to the central DVR/NVR location using wire clips or PVC casing.", "is_key_step": true, "step_number": 2}, {"title": "System Connection &amp; Power Up", "description": "BNC/RJ45 connectors are crimped and connected to the cameras and the recording unit. Power supplies are securely connected and tested.", "is_key_step": false, "step_number": 3}, {"title": "DVR/NVR Configuration", "description": "The hard drive is formatted, and recording parameters (resolution, frame rate, motion triggers) are configured in the DVR/NVR interface.", "is_key_step": true, "step_number": 4}, {"title": "Mobile App Pairing &amp; Handover", "description": "The security system is connected to the home router, and the manufacturer's app is installed and paired on the customer's phone for live viewing.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Wipe camera lenses monthly with a microfiber cloth to ensure clear night vision", "Regularly check the DVR/NVR storage to ensure older footage is overwriting correctly", "Keep the DVR/NVR in a well-ventilated area to prevent hard drive overheating"]}, {"type": "tools_materials", "tools": ["Impact drill machine and masonry drill bits", "Cable crimping tools (RJ45/BNC) and wire strippers", "Digital multimeter for power testing", "Ladder, wire clips, rawl plugs, and mounting screws", "Portable test monitor for angle adjustments"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure the cameras, DVR/NVR, hard drive, and cables are ready before the technician arrives", "Provide access to a working power socket near the DVR/NVR location", "Have your Wi-Fi password ready for network and mobile app configuration"]}, {"type": "expected_results", "items": ["All cameras firmly mounted with clear, unobstructed fields of view", "Continuous or motion-triggered video reliably recording to the hard drive", "Instant access to live camera feeds on the customer's smartphone"]}, {"type": "important_notes", "items": ["For heights exceeding 10 feet, the customer must arrange suitable scaffolding or safely secure long ladders", "Drilling through heavily reinforced concrete beams may require specialized equipment not covered in standard installation"]}, {"type": "warranty", "details": "30-day SmartServe warranty on wiring integrity and camera mounting stability", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation-only service. You must purchase the cameras, DVR/NVR, hard drive, and cables separately.", "question": "Does this service include the cost of the CCTV cameras?"}, {"answer": "Yes, if your TV is near the DVR/NVR, the technician will connect it via HDMI/VGA. If it is in another room, additional long-distance cabling is required.", "question": "Can the technician help me view the cameras on my TV?"}, {"answer": "Standard through-wall drilling (up to 8 inches) is included. However, deep core cutting or concealed in-wall routing is excluded.", "question": "What happens if the cable needs to run through a thick wall?"}, {"answer": "Most modern CCTV brands provide a free cloud P2P app for remote viewing. You only need an active internet connection at home.", "question": "Is the mobile app viewing free?"}]}, {"type": "tips", "items": ["Enable push notifications on your mobile app only for motion in specific critical zones to avoid alert fatigue.", "Install a small UPS for your DVR and router so cameras keep recording during power cuts."]}, {"dos": ["Mount cameras high enough to prevent easy tampering or vandalism", "Use outdoor-rated (IP67) cameras for any exterior installations"], "type": "dos_donts", "donts": ["Don't point cameras directly at bright light sources (like streetlights) which can cause glare", "Don't install the DVR/NVR in a locked, unventilated cabinet where it can overheat"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T13:40:49.273929+00:00</t>
+          <t>2026-09-05T14:33:06.730975+00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T13:40:49.273929+00:00</t>
+          <t>2026-09-05T14:33:06.730975+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0e851c0a-84d4-5afb-ae7d-0e0c2437e626</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.737713+00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.737713+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ade4e808-0a25-57d1-aedf-ce4675b91799</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.741411+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.741411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5bde4e4d-cdb9-55ec-9ab8-37292638bffa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.745310+00:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.745310+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a69d6500-8c3d-5141-9372-0a7948e42b6e</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.748529+00:00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.748529+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9568064a-7915-5aa9-ae1a-f94af8e1fc12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.753126+00:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.753126+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d2f0b4d6-9668-51e3-b38a-fee45502db49</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems Service Variation 7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Alarm &amp; Sensor Systems</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.756948+00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.756948+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a67d4f70-245d-5813-9d48-9fd288e1dbce</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.759898+00:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.759898+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>66075a60-6209-592c-8f05-88c118937c5d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.762855+00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.762855+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4e3e71a2-a412-5605-af49-fc63375f93b6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.765493+00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.765493+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4ff11f6d-96bf-5327-a8e4-dd961adcd046</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.768448+00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.768448+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6fea0268-604f-519a-ad5c-abdfd1a729fd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.772526+00:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.772526+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8b8c479d-6a45-5786-b4ab-25221ac13a69</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.775779+00:00</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.775779+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ca6d27c1-08c7-5464-9667-5a710ee21ca3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation Service Variation 7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CCTV/Camera Installation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.779273+00:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.779273+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>e2f0890f-da86-515c-bac5-bd65bc73b5d9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches Service Variation 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.782841+00:00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.782841+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>78f4f8dd-d22b-5c0f-b200-48bfe3f7d7d3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches Service Variation 2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.787881+00:00</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.787881+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11e176e7-7858-5027-a21b-254ee0a13f5b</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches Service Variation 3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.792484+00:00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.792484+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>228282a0-e1db-5968-9075-7aadeeffd9d9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches Service Variation 4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.796562+00:00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.796562+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>44bdaeee-a1bd-57b2-a909-3d3e7f7a977e</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches Service Variation 5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Smart Lighting/Switches</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.800784+00:00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.800784+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>95f80990-65e5-50cf-94bd-69c75aaa4e69</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.809709+00:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.809709+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>37ab940a-b8b6-59f4-a683-d15ae462f3af</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.813203+00:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.813203+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>65b4eb53-7577-519d-b48a-2bd16e49e717</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.816270+00:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.816270+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>92cd5608-ff4f-5707-bf92-a1c30a111b06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.820376+00:00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.820376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7570d619-e759-5651-afe6-f797e3dacc05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.824135+00:00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.824135+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>37a1f344-ab86-5ebf-869c-9e26f805cb1d</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control Service Variation 6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Smart Locks &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.827218+00:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.827218+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>498d667b-30bc-57fa-b3d2-7d7b1d46408f</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Video Doorbells Service Variation 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Video Doorbells</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.830339+00:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.830339+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>f7b119f9-13b1-59f1-98e7-62a8a8d9273f</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Video Doorbells Service Variation 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Video Doorbells</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.834067+00:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.834067+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>37cfa6a0-7a1d-52f2-9505-8c13fb818728</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Video Doorbells Service Variation 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Video Doorbells</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.839062+00:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.839062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>b24100aa-9570-547f-98cd-5d68c66dbddb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Video Doorbells Service Variation 4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Video Doorbells</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.842148+00:00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.842148+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8e6d6f16-3511-5e08-bc92-35f12025e142</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Video Doorbells Service Variation 5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6. Smart Home &amp; Security</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Video Doorbells</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.845213+00:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:33:06.845213+00:00</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category6_smart_home_security_FINAL.xlsx
+++ b/backend/backups/category6_smart_home_security_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,715 +425,778 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b542de45-1772-55c6-831a-1857e2534465</t>
+          <t>92cd5608-ff4f-5707-bf92-a1c30a111b06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 1</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>Automatic RFID Boom Barrier Gate Installation</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1200</v>
+        <v>3499</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing motorized gate barrier arm for apartment complexes with vehicle windshield RFID tags.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Automatic RFID Boom Barrier Gate Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Automatic RFID Boom Barrier Gate Installation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.730975+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.730975+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Automatic RFID Boom Barrier Gate Installation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0e851c0a-84d4-5afb-ae7d-0e0c2437e626</t>
+          <t>9568064a-7915-5aa9-ae1a-f94af8e1fc12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 2</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>Biometric Access Control Keypad for Offices</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1400</v>
+        <v>1899</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Setting up wall-mounted fingerprint &amp; punch card attendance access system for commercial doors.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Biometric Access Control Keypad for Offices procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Biometric Access Control Keypad for Offices procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.737713+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.737713+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Biometric Access Control Keypad for Offices take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ade4e808-0a25-57d1-aedf-ce4675b91799</t>
+          <t>a69d6500-8c3d-5141-9372-0a7948e42b6e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 3</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>High-Decibel Smart Security Siren Integration</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1600</v>
+        <v>599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wiring 110dB indoor/outdoor flashing strobe siren triggered by door intrusion or panic buttons.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional High-Decibel Smart Security Siren Integration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete High-Decibel Smart Security Siren Integration procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.741411+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.741411+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does High-Decibel Smart Security Siren Integration take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5bde4e4d-cdb9-55ec-9ab8-37292638bffa</t>
+          <t>a67d4f70-245d-5813-9d48-9fd288e1dbce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 4</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>Multi-Flat Apartment Intercom System Setup</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1800</v>
+        <v>2499</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wiring central security guard console to individual flat intercom handsets across multiple floors.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Multi-Flat Apartment Intercom System Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Multi-Flat Apartment Intercom System Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.745310+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.745310+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Multi-Flat Apartment Intercom System Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a69d6500-8c3d-5141-9372-0a7948e42b6e</t>
+          <t>ade4e808-0a25-57d1-aedf-ce4675b91799</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 5</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>Photoelectric Beam Perimeter Security Barrier</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2000</v>
+        <v>1699</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing dual infrared beam sensors across compound boundary walls detecting fence intruders.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Photoelectric Beam Perimeter Security Barrier procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Photoelectric Beam Perimeter Security Barrier procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.748529+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.748529+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Photoelectric Beam Perimeter Security Barrier take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9568064a-7915-5aa9-ae1a-f94af8e1fc12</t>
+          <t>95f80990-65e5-50cf-94bd-69c75aaa4e69</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 6</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Access &amp; Automation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>Smart Motorized Garage Door Controller Fitting</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Connecting remote wireless opener and safety photo-eye sensors for roll-up garage shutter doors.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Motorized Garage Door Controller Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Motorized Garage Door Controller Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.753126+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.753126+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Smart Motorized Garage Door Controller Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d2f0b4d6-9668-51e3-b38a-fee45502db49</t>
+          <t>8b8c479d-6a45-5786-b4ab-25221ac13a69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems Service Variation 7</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alarm &amp; Sensor Systems</t>
+          <t>4-Channel DVR / NVR Storage &amp; Remote Viewing Sync</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2400</v>
+        <v>1299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing Hard Disk Drive into DVR/NVR, crimping BNC/RJ45 cables, and configuring live phone viewing.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional 4-Channel DVR / NVR Storage &amp; Remote Viewing Sync procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional alarm &amp; sensor systems service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Alarm &amp; Sensor Systems setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 4-Channel DVR / NVR Storage &amp; Remote Viewing Sync procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.756948+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.756948+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does 4-Channel DVR / NVR Storage &amp; Remote Viewing Sync take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a67d4f70-245d-5813-9d48-9fd288e1dbce</t>
+          <t>8e6d6f16-3511-5e08-bc92-35f12025e142</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 1</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Concealed Wall Wire Conduit Camera Installation</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Chipping wall channel to lay hidden CCTV power lines for a clean aesthetic finish without visible wires.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Concealed Wall Wire Conduit Camera Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Concealed Wall Wire Conduit Camera Installation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.759898+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.759898+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Concealed Wall Wire Conduit Camera Installation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>66075a60-6209-592c-8f05-88c118937c5d</t>
+          <t>78f4f8dd-d22b-5c0f-b200-48bfe3f7d7d3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 2</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Dual-Way Video Door Phone Monitor Fitting</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1400</v>
+        <v>1499</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing outdoor camera unit at gate and indoor 7-inch color display monitor for visitor screening.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Dual-Way Video Door Phone Monitor Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dual-Way Video Door Phone Monitor Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.762855+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.762855+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Dual-Way Video Door Phone Monitor Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4e3e71a2-a412-5605-af49-fc63375f93b6</t>
+          <t>6fea0268-604f-519a-ad5c-abdfd1a729fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 3</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Indoor 360° Wi-Fi Security Camera Installation</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1600</v>
+        <v>499</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Ceiling mounting dome camera with pan-tilt-zoom features, motion tracking, and SD card configuration.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Indoor 360° Wi-Fi Security Camera Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Indoor 360° Wi-Fi Security Camera Installation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.765493+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.765493+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Indoor 360° Wi-Fi Security Camera Installation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4ff11f6d-96bf-5327-a8e4-dd961adcd046</t>
+          <t>66075a60-6209-592c-8f05-88c118937c5d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 4</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Outdoor Weatherproof HD Security Camera Fitting</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1800</v>
+        <v>799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wall mounting IP67 waterproof bullet camera, routing power cable, and adjusting night-vision angle.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Outdoor Weatherproof HD Security Camera Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Outdoor Weatherproof HD Security Camera Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.768448+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.768448+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Outdoor Weatherproof HD Security Camera Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6fea0268-604f-519a-ad5c-abdfd1a729fd</t>
+          <t>7570d619-e759-5651-afe6-f797e3dacc05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 5</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Home Security</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Wireless Motion Sensor Burglar Alarm Setup</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2000</v>
+        <v>899</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Placing PIR motion detectors, pairing wireless siren hub, and setting up automated smartphone alert calls.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Wireless Motion Sensor Burglar Alarm Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Wireless Motion Sensor Burglar Alarm Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.772526+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.772526+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Wireless Motion Sensor Burglar Alarm Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8b8c479d-6a45-5786-b4ab-25221ac13a69</t>
+          <t>e2f0890f-da86-515c-bac5-bd65bc73b5d9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 6</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Air Quality &amp; Dust Sensor Smart Integration</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2200</v>
+        <v>499</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Setting up indoor PM2.5 / VOC monitor linked to auto-turn on smart air purifiers.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Air Quality &amp; Dust Sensor Smart Integration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Air Quality &amp; Dust Sensor Smart Integration procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.775779+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.775779+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Air Quality &amp; Dust Sensor Smart Integration take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1162,845 +1208,930 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation Service Variation 7</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CCTV/Camera Installation</t>
+          <t>Magnetic Door &amp; Window Open/Close Sensor Setup</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2400</v>
+        <v>399</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Sticking wireless reed magnetic contacts on main doors and balconies for entrance logs.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Magnetic Door &amp; Window Open/Close Sensor Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cctv/camera installation service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert CCTV/Camera Installation setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Magnetic Door &amp; Window Open/Close Sensor Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.779273+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.779273+00:00</t>
+          <t>[{'answer': 'The session typically takes around 25 minutes.', 'question': 'How long does Magnetic Door &amp; Window Open/Close Sensor Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e2f0890f-da86-515c-bac5-bd65bc73b5d9</t>
+          <t>b24100aa-9570-547f-98cd-5d68c66dbddb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches Service Variation 1</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches</t>
+          <t>Smart LPG / Natural Gas Leak Detector Fitting</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1200</v>
+        <v>599</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Fixing catalytic gas sensor near kitchen cylinder with auto shut-off solenoid valve trigger.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart LPG / Natural Gas Leak Detector Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart LPG / Natural Gas Leak Detector Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.782841+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.782841+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Smart LPG / Natural Gas Leak Detector Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>78f4f8dd-d22b-5c0f-b200-48bfe3f7d7d3</t>
+          <t>b542de45-1772-55c6-831a-1857e2534465</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches Service Variation 2</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches</t>
+          <t>Smart Water Flood &amp; Pipe Leak Sensor Setup</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1400</v>
+        <v>499</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Placing probe sensors near washing machines and water purifiers to alert before home flooding occurs.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Water Flood &amp; Pipe Leak Sensor Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Water Flood &amp; Pipe Leak Sensor Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.787881+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.787881+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Smart Water Flood &amp; Pipe Leak Sensor Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11e176e7-7858-5027-a21b-254ee0a13f5b</t>
+          <t>d2f0b4d6-9668-51e3-b38a-fee45502db49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches Service Variation 3</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches</t>
+          <t>Smart Wi-Fi Digital Thermostat Installation</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1600</v>
+        <v>899</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Replacing manual AC control with smart touchscreen thermostat maintaining scheduled room temps.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Wi-Fi Digital Thermostat Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Wi-Fi Digital Thermostat Installation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.792484+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.792484+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Smart Wi-Fi Digital Thermostat Installation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>228282a0-e1db-5968-9075-7aadeeffd9d9</t>
+          <t>f7b119f9-13b1-59f1-98e7-62a8a8d9273f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches Service Variation 4</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Sensor &amp; Monitoring</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches</t>
+          <t>Solar PIR Motion Security Floodlight Setup</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1800</v>
+        <v>699</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Mounting outdoor solar-powered LED floodlight that illuminates automatically when human motion is detected.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Solar PIR Motion Security Floodlight Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Solar PIR Motion Security Floodlight Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.796562+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.796562+00:00</t>
+          <t>[{'answer': 'The session typically takes around 40 minutes.', 'question': 'How long does Solar PIR Motion Security Floodlight Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>44bdaeee-a1bd-57b2-a909-3d3e7f7a977e</t>
+          <t>65b4eb53-7577-519d-b48a-2bd16e49e717</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches Service Variation 5</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Smart Lighting/Switches</t>
+          <t>Centralized Smart Gateway &amp; Zigbee Router Setup</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2000</v>
+        <v>899</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Setting up local Zigbee 3.0 gateway hub ensuring seamless offline mesh connectivity for all smart sensors.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Centralized Smart Gateway &amp; Zigbee Router Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart lighting/switches service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Lighting/Switches setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Centralized Smart Gateway &amp; Zigbee Router Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.800784+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.800784+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Centralized Smart Gateway &amp; Zigbee Router Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>95f80990-65e5-50cf-94bd-69c75aaa4e69</t>
+          <t>4ff11f6d-96bf-5327-a8e4-dd961adcd046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 1</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Heavy-Duty Smart Plug (16A) AC/Geyser Sync</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1200</v>
+        <v>349</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing 16 Amp high-power smart plugs for heavy appliances with power consumption monitoring.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Heavy-Duty Smart Plug (16A) AC/Geyser Sync procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Heavy-Duty Smart Plug (16A) AC/Geyser Sync procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.809709+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.809709+00:00</t>
+          <t>[{'answer': 'The session typically takes around 25 minutes.', 'question': 'How long does Heavy-Duty Smart Plug (16A) AC/Geyser Sync take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>37ab940a-b8b6-59f4-a683-d15ae462f3af</t>
+          <t>4e3e71a2-a412-5605-af49-fc63375f93b6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 2</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Motorized Smart Curtain Rod &amp; Motor Setup</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1400</v>
+        <v>1299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Fixing electric curtain track on ceiling, mounting heavy-duty motor, and programming timer schedules.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Motorized Smart Curtain Rod &amp; Motor Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Motorized Smart Curtain Rod &amp; Motor Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.813203+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.813203+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Motorized Smart Curtain Rod &amp; Motor Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>65b4eb53-7577-519d-b48a-2bd16e49e717</t>
+          <t>498d667b-30bc-57fa-b3d2-7d7b1d46408f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 3</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Smart Dimmer &amp; RGB Ambient Lighting Controller</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1600</v>
+        <v>499</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wiring smart strip light controllers, false ceiling LED dimmers, and pairing with mobile app scenes.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Dimmer &amp; RGB Ambient Lighting Controller procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Dimmer &amp; RGB Ambient Lighting Controller procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.816270+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.816270+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Smart Dimmer &amp; RGB Ambient Lighting Controller take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>92cd5608-ff4f-5707-bf92-a1c30a111b06</t>
+          <t>44bdaeee-a1bd-57b2-a909-3d3e7f7a977e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 4</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Smart Wi-Fi Switchboard Retrofit Fitting</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1800</v>
+        <v>599</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing modular smart switch relays behind existing wall switchboards for app control of lights &amp; fans.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Wi-Fi Switchboard Retrofit Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Wi-Fi Switchboard Retrofit Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.820376+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.820376+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Smart Wi-Fi Switchboard Retrofit Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7570d619-e759-5651-afe6-f797e3dacc05</t>
+          <t>5bde4e4d-cdb9-55ec-9ab8-37292638bffa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 5</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Home Devices</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Voice Assistant Hub Integration (Alexa / Google)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2000</v>
+        <v>699</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuring Amazon Echo / Google Nest hub, grouping rooms, and creating custom voice routines.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Voice Assistant Hub Integration (Alexa / Google) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Voice Assistant Hub Integration (Alexa / Google) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.824135+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.824135+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Voice Assistant Hub Integration (Alexa / Google) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>37a1f344-ab86-5ebf-869c-9e26f805cb1d</t>
+          <t>0e851c0a-84d4-5afb-ae7d-0e0c2437e626</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control Service Variation 6</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Smart Locks &amp; Access Control</t>
+          <t>Biometric Fingerprint Smart Door Lock Fitting</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2200</v>
+        <v>1499</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Professional installation of main wooden door biometric fingerprint, RFID card, and passcode mortise lock.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Biometric Fingerprint Smart Door Lock Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional smart locks &amp; access control service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Smart Locks &amp; Access Control setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Biometric Fingerprint Smart Door Lock Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.827218+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.827218+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Biometric Fingerprint Smart Door Lock Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>498d667b-30bc-57fa-b3d2-7d7b1d46408f</t>
+          <t>37cfa6a0-7a1d-52f2-9505-8c13fb818728</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Video Doorbells Service Variation 1</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Video Doorbells</t>
+          <t>Bluetooth Smart Latch &amp; Mortise Setup</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1200</v>
+        <v>1099</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Fitting compact Bluetooth smart rim latch suitable for bedroom doors with phone auto-unlock feature.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Bluetooth Smart Latch &amp; Mortise Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Bluetooth Smart Latch &amp; Mortise Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.830339+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.830339+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Bluetooth Smart Latch &amp; Mortise Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f7b119f9-13b1-59f1-98e7-62a8a8d9273f</t>
+          <t>228282a0-e1db-5968-9075-7aadeeffd9d9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Video Doorbells Service Variation 2</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Video Doorbells</t>
+          <t>Keyless Touchscreen Digital Lock Fitting</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400</v>
+        <v>1299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Chiseling door frame and fitting keyless PIN code digital lock with emergency mechanical key backup.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Keyless Touchscreen Digital Lock Fitting procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Keyless Touchscreen Digital Lock Fitting procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.834067+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.834067+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Keyless Touchscreen Digital Lock Fitting take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>37cfa6a0-7a1d-52f2-9505-8c13fb818728</t>
+          <t>37a1f344-ab86-5ebf-869c-9e26f805cb1d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Video Doorbells Service Variation 3</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Video Doorbells</t>
+          <t>RFID Card Keyless Access Lock Installation</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1600</v>
+        <v>999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing tap-to-enter RFID card lock for glass office doors or residential apartment entry doors.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional RFID Card Keyless Access Lock Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete RFID Card Keyless Access Lock Installation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.839062+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.839062+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does RFID Card Keyless Access Lock Installation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b24100aa-9570-547f-98cd-5d68c66dbddb</t>
+          <t>37ab940a-b8b6-59f4-a683-d15ae462f3af</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Video Doorbells Service Variation 4</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Video Doorbells</t>
+          <t>Smart Lock Battery Replacement &amp; Diagnostics</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1800</v>
+        <v>399</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Troubleshooting unresponsive digital locks, replacing AA/lithium batteries, and recalibrating sensors.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Lock Battery Replacement &amp; Diagnostics procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Lock Battery Replacement &amp; Diagnostics procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.842148+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.842148+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Smart Lock Battery Replacement &amp; Diagnostics take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8e6d6f16-3511-5e08-bc92-35f12025e142</t>
+          <t>11e176e7-7858-5027-a21b-254ee0a13f5b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Video Doorbells Service Variation 5</t>
+          <t>6. Smart Home &amp; Security</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6. Smart Home &amp; Security</t>
+          <t>Smart Locks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Video Doorbells</t>
+          <t>Smart Video Doorbell &amp; Lock Sync Setup</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2000</v>
+        <v>1199</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Mounting HD video doorbell, connecting to home Wi-Fi, and linking with electronic door lock app.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Standard installation", "Basic setup and testing", "Clean up post-service", "System demonstration"]</t>
+          <t>['Professional Smart Video Doorbell &amp; Lock Sync Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional video doorbells service for your smart home.", "type": "description"}, {"type": "highlights", "items": ["Expert Video Doorbells setup", "Secure configuration", "Post-installation demo", "24/7 Support available"]}, {"type": "excluded_scope", "items": ["Major structural modifications", "Cost of equipment (unless specified)"]}, {"type": "process_steps", "steps": [{"title": "Inspection", "description": "Site inspection for optimal placement", "step_number": 1}, {"title": "Installation", "description": "Mounting and wiring of the device", "step_number": 2}, {"title": "Configuration", "description": "Connecting the device to the smart network", "step_number": 3}, {"title": "Testing", "description": "Functional testing and system verification", "step_number": 4}, {"title": "Handover", "description": "Demonstrating usage and safety guidelines to the customer", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Do not touch exposed wiring before setup is complete", "Keep devices clean from dust"]}, {"type": "tools_materials", "tools": ["Drill machine", "Screwdrivers", "Wire strippers", "Mounting hardware"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure Wi-Fi availability", "Provide access to installation points"]}, {"type": "expected_results", "items": "Fully functional smart home system."}, {"type": "important_notes", "items": "Wi-Fi connectivity issues are not covered under installation warranty."}, {"type": "warranty", "details": "30 days service warranty.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No, this is an installation service only unless specified.", "question": "Do you provide the devices?"}, {"answer": "Typically 1 to 2 hours depending on complexity.", "question": "How long does the installation take?"}, {"answer": "Yes, someone needs to be present to grant access and verify the setup.", "question": "Do I need to be home during the service?"}, {"answer": "Yes, we provide a 30-day service warranty on our work.", "question": "Is the installation covered by warranty?"}]}, {"type": "tips", "items": ["Change default passwords immediately after setup."]}, {"dos": ["Connect devices to a secure network."], "type": "dos_donts", "donts": ["Do not expose indoor cameras to outdoor environments."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart Video Doorbell &amp; Lock Sync Setup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.845213+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:33:06.845213+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Smart Video Doorbell &amp; Lock Sync Setup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
